--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_один эксперт.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Эксперт_оценки MoSCoW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_итог" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица_взаимосвязей_FR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Четкий MoSCoW_итог" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -162,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -192,21 +193,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -596,12 +594,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -650,7 +648,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -667,17 +665,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -694,12 +692,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -721,7 +719,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Mo</t>
         </is>
       </c>
     </row>
@@ -738,7 +736,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -755,12 +753,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -777,7 +775,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -787,7 +785,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -804,12 +802,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -821,17 +819,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mo</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -848,12 +846,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
         </is>
       </c>
     </row>
@@ -873,50 +871,512 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
+          <t>Матрица взаимосвязанности функциональных требований</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
           <t>Четкий MoSCoW — итоговая приоритизация (один эксперт)</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>1) Нефункциональные требования (NFR) и их веса</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>NFR</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Приоритет NFR</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Вес NFR</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>NFR1</t>
         </is>
@@ -926,478 +1386,668 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="C5" s="14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>NFR2</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>NFR3</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>2) Расчет PFR по функциональным требованиям (FR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>NFR1</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>NFR2</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>NFR3</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>PFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>21.28</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>NFR3</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="E15" s="14" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>3) Итоговая сортировка FR по убыванию PFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>PFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>21.28</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>2) Расчет PFR по функциональным требованиям (FR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>FR3</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1"/>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>4) Скорректированный рейтинг FR с учетом взаимосвязанности</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Место</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>NFR1</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>NFR2</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>NFR3</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>PFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Исходный PFR</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Скорректированный PFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>14.15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="C37" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>FR4</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>FR8</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>FR10</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>FR9</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>6.600000000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="C42" s="14" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>13.28</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>FR5</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>FR7</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>FR6</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>FR4</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>12.45</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>FR5</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>10.75</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>FR6</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>FR7</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>FR8</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>12.45</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>FR9</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>10.75</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>FR10</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Co</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Mo</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>8.275</v>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>3) Итоговая сортировка FR по убыванию PFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Место</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>PFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>FR1</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>14.15</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>FR4</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="n">
-        <v>12.45</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>FR8</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n">
-        <v>12.45</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>FR6</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="n">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>FR7</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>FR5</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="n">
-        <v>10.75</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>FR9</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>10.75</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>FR3</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="n">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>FR10</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>8.275</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="n">
-        <v>6.600000000000001</v>
+      <c r="C46" s="14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>5.28</v>
       </c>
     </row>
   </sheetData>

--- a/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_один эксперт.xlsx
+++ b/2026.02.16_Файлы загрузки и выгрузки данных/Итоги_четкий MoSCoW_один эксперт.xlsx
@@ -163,15 +163,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,6 +183,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -198,13 +198,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -553,14 +556,14 @@
   <dimension ref="A3:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="30.85546875" customWidth="1" min="1" max="1"/>
     <col width="11.42578125" customWidth="1" min="2" max="2"/>
     <col width="12.140625" customWidth="1" min="3" max="3"/>
     <col width="11.7109375" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Нефункциональное требование (англ. Non-functional requirements, NFR)</t>
         </is>
@@ -582,22 +585,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Приоритет нефункционального требования</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -636,220 +639,220 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FR1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>FR3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>FR4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FR5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FR6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FR7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FR8</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FR9</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FR10</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Co</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Mo</t>
         </is>
@@ -874,7 +877,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1336,8 +1339,8 @@
   <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -1346,7 +1349,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Четкий MoSCoW — итоговая приоритизация (один эксперт)</t>
+          <t>Четкий MoSCoW - итоговая приоритизация (один эксперт)</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1389,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1401,7 +1404,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1416,7 +1419,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1476,7 +1479,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="17" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1501,7 +1504,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="17" t="n">
         <v>13.28</v>
       </c>
     </row>
@@ -1526,7 +1529,7 @@
           <t>W</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="17" t="n">
         <v>5.28</v>
       </c>
     </row>
@@ -1551,7 +1554,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="17" t="n">
         <v>21.28</v>
       </c>
     </row>
@@ -1576,7 +1579,7 @@
           <t>S</t>
         </is>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="17" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -1601,7 +1604,7 @@
           <t>Co</t>
         </is>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="17" t="n">
         <v>7.92</v>
       </c>
     </row>
@@ -1626,7 +1629,7 @@
           <t>W</t>
         </is>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="17" t="n">
         <v>10.56</v>
       </c>
     </row>
@@ -1651,7 +1654,7 @@
           <t>S</t>
         </is>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="17" t="n">
         <v>15.84</v>
       </c>
     </row>
@@ -1676,7 +1679,7 @@
           <t>W</t>
         </is>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1701,7 +1704,7 @@
           <t>Mo</t>
         </is>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="17" t="n">
         <v>13.28</v>
       </c>
     </row>
@@ -1739,7 +1742,7 @@
           <t>FR1</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="17" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1752,7 +1755,7 @@
           <t>FR4</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>21.28</v>
       </c>
     </row>
@@ -1765,7 +1768,7 @@
           <t>FR8</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>15.84</v>
       </c>
     </row>
@@ -1778,7 +1781,7 @@
           <t>FR2</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>13.28</v>
       </c>
     </row>
@@ -1791,7 +1794,7 @@
           <t>FR10</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>13.28</v>
       </c>
     </row>
@@ -1804,7 +1807,7 @@
           <t>FR5</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="17" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -1817,7 +1820,7 @@
           <t>FR7</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="17" t="n">
         <v>10.56</v>
       </c>
     </row>
@@ -1830,7 +1833,7 @@
           <t>FR6</t>
         </is>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="17" t="n">
         <v>7.92</v>
       </c>
     </row>
@@ -1843,7 +1846,7 @@
           <t>FR3</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C32" s="17" t="n">
         <v>5.28</v>
       </c>
     </row>
@@ -1856,7 +1859,7 @@
           <t>FR9</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1899,10 +1902,10 @@
           <t>FR1</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
+      <c r="C37" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D37" s="17" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1915,10 +1918,10 @@
           <t>FR4</t>
         </is>
       </c>
-      <c r="C38" s="14" t="n">
+      <c r="C38" s="17" t="n">
         <v>21.28</v>
       </c>
-      <c r="D38" s="14" t="n">
+      <c r="D38" s="17" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1931,10 +1934,10 @@
           <t>FR8</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C39" s="17" t="n">
         <v>15.84</v>
       </c>
-      <c r="D39" s="14" t="n">
+      <c r="D39" s="17" t="n">
         <v>15.84</v>
       </c>
     </row>
@@ -1947,10 +1950,10 @@
           <t>FR10</t>
         </is>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C40" s="17" t="n">
         <v>13.28</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="17" t="n">
         <v>15.84</v>
       </c>
     </row>
@@ -1963,10 +1966,10 @@
           <t>FR9</t>
         </is>
       </c>
-      <c r="C41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="14" t="n">
+      <c r="C41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="17" t="n">
         <v>15.84</v>
       </c>
     </row>
@@ -1979,10 +1982,10 @@
           <t>FR2</t>
         </is>
       </c>
-      <c r="C42" s="14" t="n">
+      <c r="C42" s="17" t="n">
         <v>13.28</v>
       </c>
-      <c r="D42" s="14" t="n">
+      <c r="D42" s="17" t="n">
         <v>13.28</v>
       </c>
     </row>
@@ -1995,10 +1998,10 @@
           <t>FR5</t>
         </is>
       </c>
-      <c r="C43" s="14" t="n">
+      <c r="C43" s="17" t="n">
         <v>13.2</v>
       </c>
-      <c r="D43" s="14" t="n">
+      <c r="D43" s="17" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -2011,10 +2014,10 @@
           <t>FR7</t>
         </is>
       </c>
-      <c r="C44" s="14" t="n">
+      <c r="C44" s="17" t="n">
         <v>10.56</v>
       </c>
-      <c r="D44" s="14" t="n">
+      <c r="D44" s="17" t="n">
         <v>10.56</v>
       </c>
     </row>
@@ -2027,10 +2030,10 @@
           <t>FR6</t>
         </is>
       </c>
-      <c r="C45" s="14" t="n">
+      <c r="C45" s="17" t="n">
         <v>7.92</v>
       </c>
-      <c r="D45" s="14" t="n">
+      <c r="D45" s="17" t="n">
         <v>10.56</v>
       </c>
     </row>
@@ -2043,10 +2046,10 @@
           <t>FR3</t>
         </is>
       </c>
-      <c r="C46" s="14" t="n">
+      <c r="C46" s="17" t="n">
         <v>5.28</v>
       </c>
-      <c r="D46" s="14" t="n">
+      <c r="D46" s="17" t="n">
         <v>5.28</v>
       </c>
     </row>
